--- a/lnko.xlsx
+++ b/lnko.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MolnárBeatrixKatalin\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MolnárBeatrixKatalin\Documents\03_04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC9C70B5-D3DB-473D-9EE0-CC569FDAC780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465CC32B-AB48-4255-A32F-D226F851CEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{C82C0B8D-1883-406A-AB32-503BB4880FA1}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="25">
   <si>
     <t>a</t>
   </si>
@@ -70,6 +70,48 @@
   </si>
   <si>
     <t>lnko</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>ki:5</t>
+  </si>
+  <si>
+    <t>ki:12</t>
+  </si>
+  <si>
+    <t>ki:16</t>
+  </si>
+  <si>
+    <t>szam</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>szam% i!==0</t>
+  </si>
+  <si>
+    <t>i&gt;math.sqrt(szam)</t>
+  </si>
+  <si>
+    <t>sqrt(szam)&lt;=i</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>sqrt(szam)&gt;=i</t>
   </si>
 </sst>
 </file>
@@ -115,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -126,6 +168,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -194,6 +240,116 @@
         <a:ln>
           <a:solidFill>
             <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>456136</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Kép 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05C7AAA4-7398-416B-A851-0A57EAAAF83C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4381500"/>
+          <a:ext cx="4113736" cy="2781300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>130137</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Kép 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A0ED421-BF69-4436-862D-A99E6A0F12B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7429500"/>
+          <a:ext cx="7258050" cy="2225637"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -500,17 +656,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85660BF6-8856-48A9-8EB0-F48C5458AB7A}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="15" max="15" width="7.85546875" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -720,6 +882,290 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
+    </row>
+    <row r="25" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I26">
+        <v>14</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>754</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27">
+        <v>4</v>
+      </c>
+      <c r="M27">
+        <v>75</v>
+      </c>
+      <c r="N27">
+        <v>4</v>
+      </c>
+      <c r="O27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>5</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>7</v>
+      </c>
+      <c r="N28">
+        <v>9</v>
+      </c>
+      <c r="O28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>16</v>
+      </c>
+      <c r="O29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I31">
+        <v>624</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I32">
+        <v>62</v>
+      </c>
+      <c r="J32">
+        <v>4</v>
+      </c>
+      <c r="K32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="I33">
+        <v>6</v>
+      </c>
+      <c r="J33">
+        <v>6</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>12</v>
+      </c>
+      <c r="K34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="I35" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="N40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="N41" s="3">
+        <v>6</v>
+      </c>
+      <c r="O41" s="3">
+        <v>2</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="N43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="N44" s="3">
+        <v>5</v>
+      </c>
+      <c r="O44" s="3">
+        <v>2</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="N45" s="3"/>
+      <c r="O45" s="3">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="9:19" x14ac:dyDescent="0.25">
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="49" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N50">
+        <v>3</v>
+      </c>
+      <c r="O50" s="3">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
